--- a/file_upload_forms/034_functional_behavior_assessment--file_upload_forms.xlsx
+++ b/file_upload_forms/034_functional_behavior_assessment--file_upload_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
